--- a/Capítulo02/Capítulo02/LAN HOUSE.xlsx
+++ b/Capítulo02/Capítulo02/LAN HOUSE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="21231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Silvia\Documents\Livro Excel 2019\Avançado\Excel 2019\Planilhas\DO CURSO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://senacspedu-my.sharepoint.com/personal/yuri_smendes_senacsp_edu_br/Documents/Capítulo02/Capítulo02/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA5AE9B3-CA6C-4F79-98F7-8BCCADC4BD78}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="107" documentId="13_ncr:1_{EA5AE9B3-CA6C-4F79-98F7-8BCCADC4BD78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5EC7BA78-A906-4F98-820F-11C0AAD6FA09}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,12 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -30,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>HORA INICIAL</t>
   </si>
@@ -84,15 +89,28 @@
   </si>
   <si>
     <t>NETHOUSE - COMPUTADOR 23 - 03/06/2018</t>
+  </si>
+  <si>
+    <t>*APLICAR 20% DE DESCONTO A PARTIR DAS 11:59 MANHÃ</t>
+  </si>
+  <si>
+    <t>FUNÇÕES</t>
+  </si>
+  <si>
+    <t>B e C para o formato hh:mm e D para [h]:mm.</t>
+  </si>
+  <si>
+    <t>#=SE(HORA(B5)&lt;=11;($B$2-$B$2*20%)/60;$B$2) - definir o valor do minuto</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="8" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="[h]:mm"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -132,12 +150,30 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -168,7 +204,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -177,24 +213,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="20" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="8" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="8" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -203,7 +231,20 @@
     <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -225,9 +266,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -265,9 +306,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -300,26 +341,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -352,26 +376,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -543,97 +550,170 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="312" row="1">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{D1BCBC00-DE17-4FFB-9803-ACC796D756AA}">
+  <we:reference id="wa200005502" version="1.0.0.13" store="pt-BR" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200005502" version="1.0.0.13" store="WA200005502" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="docId" value="&quot;3MyQkY-edUWwlPB8YTTg3&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+  <we:extLst>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{7C84B067-C214-45C3-A712-C9D94CD141B2}">
+      <we:customFunctionIdList>
+        <we:customFunctionIds>_xldudf_GPT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_CREATE_PROMPT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_LIST</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_HLIST</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_CLASSIFY</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_TRANSLATE</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_EXTRACT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_TAG</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_CONVERT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_FORMAT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_SUMMARIZE</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_TABLE</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_FILL</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_SPLIT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_HSPLIT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_EDIT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_MATCH</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_VISION</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_WEB</we:customFunctionIds>
+      </we:customFunctionIdList>
+    </a:ext>
+  </we:extLst>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="2" width="10.5703125" customWidth="1"/>
     <col min="3" max="3" width="9.140625" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" customWidth="1"/>
     <col min="5" max="5" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.85546875" style="1" customWidth="1"/>
     <col min="7" max="8" width="14.85546875" style="1" customWidth="1"/>
     <col min="9" max="9" width="12.7109375" style="2" customWidth="1"/>
+    <col min="13" max="13" width="68.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="18" t="s">
+    <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
       <c r="J1" s="6"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="8">
         <v>10</v>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="7"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="10"/>
     </row>
-    <row r="4" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M3" s="15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="15" t="s">
+      <c r="F4" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="15" t="s">
+      <c r="G4" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="15" t="s">
+      <c r="H4" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="I4" s="16" t="s">
+      <c r="I4" s="12" t="s">
         <v>5</v>
       </c>
+      <c r="M4" s="17" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="4">
         <v>0.375</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="18">
         <v>0.4201388888888889</v>
       </c>
-      <c r="D5" s="8"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="17"/>
+      <c r="D5" s="4">
+        <f>C5-B5</f>
+        <v>4.5138888888888895E-2</v>
+      </c>
+      <c r="E5" s="19">
+        <f>HOUR(D5)</f>
+        <v>1</v>
+      </c>
+      <c r="F5" s="19">
+        <f>MINUTE(D5)</f>
+        <v>5</v>
+      </c>
+      <c r="G5" s="19">
+        <f>E5*60+F5</f>
+        <v>65</v>
+      </c>
+      <c r="H5" s="21">
+        <f>IF(HOUR(B5)&lt;=11,($B$2-$B$2*20%)/60,$B$2)</f>
+        <v>0.13333333333333333</v>
+      </c>
       <c r="I5" s="5"/>
+      <c r="M5" s="20" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>10</v>
       </c>
@@ -643,14 +723,29 @@
       <c r="C6" s="4">
         <v>0.44930555555555557</v>
       </c>
-      <c r="D6" s="8"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="17"/>
+      <c r="D6" s="4">
+        <f t="shared" ref="D6:D11" si="0">C6-B6</f>
+        <v>2.777777777777779E-2</v>
+      </c>
+      <c r="E6" s="19">
+        <f t="shared" ref="E6:E11" si="1">HOUR(D6)</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="19">
+        <f t="shared" ref="F6:F11" si="2">MINUTE(D6)</f>
+        <v>40</v>
+      </c>
+      <c r="G6" s="19">
+        <f t="shared" ref="G6:G11" si="3">E6*60+F6</f>
+        <v>40</v>
+      </c>
+      <c r="H6" s="13">
+        <f t="shared" ref="H6:H11" si="4">IF(HOUR(B6)&lt;=11,($B$2-$B$2*20%)/60,$B$2)</f>
+        <v>0.13333333333333333</v>
+      </c>
       <c r="I6" s="5"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>11</v>
       </c>
@@ -660,14 +755,29 @@
       <c r="C7" s="4">
         <v>0.47916666666666669</v>
       </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="17"/>
+      <c r="D7" s="4">
+        <f t="shared" si="0"/>
+        <v>2.777777777777779E-2</v>
+      </c>
+      <c r="E7" s="19">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F7" s="19">
+        <f t="shared" si="2"/>
+        <v>40</v>
+      </c>
+      <c r="G7" s="19">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="H7" s="13">
+        <f t="shared" si="4"/>
+        <v>0.13333333333333333</v>
+      </c>
       <c r="I7" s="5"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>12</v>
       </c>
@@ -677,14 +787,29 @@
       <c r="C8" s="4">
         <v>0.50347222222222221</v>
       </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="17"/>
+      <c r="D8" s="4">
+        <f t="shared" si="0"/>
+        <v>2.3611111111111083E-2</v>
+      </c>
+      <c r="E8" s="19">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F8" s="19">
+        <f t="shared" si="2"/>
+        <v>34</v>
+      </c>
+      <c r="G8" s="19">
+        <f t="shared" si="3"/>
+        <v>34</v>
+      </c>
+      <c r="H8" s="13">
+        <f t="shared" si="4"/>
+        <v>0.13333333333333333</v>
+      </c>
       <c r="I8" s="5"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>13</v>
       </c>
@@ -694,14 +819,29 @@
       <c r="C9" s="4">
         <v>0.57291666666666663</v>
       </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="17"/>
+      <c r="D9" s="4">
+        <f t="shared" si="0"/>
+        <v>6.8055555555555536E-2</v>
+      </c>
+      <c r="E9" s="19">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="F9" s="19">
+        <f t="shared" si="2"/>
+        <v>38</v>
+      </c>
+      <c r="G9" s="19">
+        <f t="shared" si="3"/>
+        <v>98</v>
+      </c>
+      <c r="H9" s="13">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
       <c r="I9" s="5"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>14</v>
       </c>
@@ -711,14 +851,29 @@
       <c r="C10" s="4">
         <v>0.6875</v>
       </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="17"/>
+      <c r="D10" s="4">
+        <f t="shared" si="0"/>
+        <v>0.11388888888888882</v>
+      </c>
+      <c r="E10" s="19">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="F10" s="19">
+        <f t="shared" si="2"/>
+        <v>44</v>
+      </c>
+      <c r="G10" s="19">
+        <f t="shared" si="3"/>
+        <v>164</v>
+      </c>
+      <c r="H10" s="13">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
       <c r="I10" s="5"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>15</v>
       </c>
@@ -728,12 +883,33 @@
       <c r="C11" s="4">
         <v>0.75</v>
       </c>
-      <c r="D11" s="8"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="17"/>
+      <c r="D11" s="4">
+        <f t="shared" si="0"/>
+        <v>5.208333333333337E-2</v>
+      </c>
+      <c r="E11" s="19">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="F11" s="19">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="G11" s="19">
+        <f t="shared" si="3"/>
+        <v>75</v>
+      </c>
+      <c r="H11" s="13">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
       <c r="I11" s="5"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="C12" s="16">
+        <f>SUM(C5:C11)</f>
+        <v>3.8624999999999998</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -763,6 +939,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100CEB2B541769F8A4991DE642272C524BB" ma:contentTypeVersion="0" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="7ae862ae5010eca0394e8ac9f072291e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="397561fba88d9dece65508bac662637b">
     <xsd:element name="properties">
@@ -876,29 +1067,35 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3023F845-B776-44D6-BD9D-EB23702C7163}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEC5D026-099B-4C5A-B95D-B86D765E2B2E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94AB0242-7A83-4BD2-8609-680DB457C9EC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94AB0242-7A83-4BD2-8609-680DB457C9EC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEC5D026-099B-4C5A-B95D-B86D765E2B2E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3023F845-B776-44D6-BD9D-EB23702C7163}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Capítulo02/Capítulo02/LAN HOUSE.xlsx
+++ b/Capítulo02/Capítulo02/LAN HOUSE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://senacspedu-my.sharepoint.com/personal/yuri_smendes_senacsp_edu_br/Documents/Capítulo02/Capítulo02/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="107" documentId="13_ncr:1_{EA5AE9B3-CA6C-4F79-98F7-8BCCADC4BD78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5EC7BA78-A906-4F98-820F-11C0AAD6FA09}"/>
+  <xr:revisionPtr revIDLastSave="112" documentId="13_ncr:1_{EA5AE9B3-CA6C-4F79-98F7-8BCCADC4BD78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C6DD741-5E0A-4D36-962C-A481213566EA}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -100,7 +100,7 @@
     <t>B e C para o formato hh:mm e D para [h]:mm.</t>
   </si>
   <si>
-    <t>#=SE(HORA(B5)&lt;=11;($B$2-$B$2*20%)/60;$B$2) - definir o valor do minuto</t>
+    <t>#=SE(HORA(B5)&lt;=11;($B$2-$B$2*20%)/60;$B$2/60) - definir o valor do minuto</t>
   </si>
 </sst>
 </file>
@@ -110,7 +110,7 @@
   <numFmts count="3">
     <numFmt numFmtId="8" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="[h]:mm"/>
+    <numFmt numFmtId="164" formatCode="[h]:mm"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -204,7 +204,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -228,23 +228,20 @@
     <xf numFmtId="44" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="2" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -570,6 +567,9 @@
   <we:bindings/>
   <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
   <we:extLst>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{D87F86FE-615C-45B5-9D79-34F1136793EB}">
+      <we:containsCustomFunctions/>
+    </a:ext>
     <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{7C84B067-C214-45C3-A712-C9D94CD141B2}">
       <we:customFunctionIdList>
         <we:customFunctionIds>_xldudf_GPT</we:customFunctionIds>
@@ -615,17 +615,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
       <c r="J1" s="6"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
@@ -642,7 +642,7 @@
       <c r="I2" s="10"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="M3" s="15" t="s">
+      <c r="M3" s="13" t="s">
         <v>19</v>
       </c>
     </row>
@@ -674,7 +674,7 @@
       <c r="I4" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="M4" s="17" t="s">
+      <c r="M4" s="15" t="s">
         <v>20</v>
       </c>
     </row>
@@ -685,31 +685,34 @@
       <c r="B5" s="4">
         <v>0.375</v>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="16">
         <v>0.4201388888888889</v>
       </c>
       <c r="D5" s="4">
         <f>C5-B5</f>
         <v>4.5138888888888895E-2</v>
       </c>
-      <c r="E5" s="19">
+      <c r="E5" s="17">
         <f>HOUR(D5)</f>
         <v>1</v>
       </c>
-      <c r="F5" s="19">
+      <c r="F5" s="17">
         <f>MINUTE(D5)</f>
         <v>5</v>
       </c>
-      <c r="G5" s="19">
+      <c r="G5" s="17">
         <f>E5*60+F5</f>
         <v>65</v>
       </c>
-      <c r="H5" s="21">
-        <f>IF(HOUR(B5)&lt;=11,($B$2-$B$2*20%)/60,$B$2)</f>
+      <c r="H5" s="19">
+        <f>IF(HOUR(B5)&lt;=11,($B$2-$B$2*20%)/60,$B$2/60)</f>
         <v>0.13333333333333333</v>
       </c>
-      <c r="I5" s="5"/>
-      <c r="M5" s="20" t="s">
+      <c r="I5" s="5">
+        <f>G5*H5</f>
+        <v>8.6666666666666661</v>
+      </c>
+      <c r="M5" s="18" t="s">
         <v>21</v>
       </c>
     </row>
@@ -727,23 +730,26 @@
         <f t="shared" ref="D6:D11" si="0">C6-B6</f>
         <v>2.777777777777779E-2</v>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="17">
         <f t="shared" ref="E6:E11" si="1">HOUR(D6)</f>
         <v>0</v>
       </c>
-      <c r="F6" s="19">
+      <c r="F6" s="17">
         <f t="shared" ref="F6:F11" si="2">MINUTE(D6)</f>
         <v>40</v>
       </c>
-      <c r="G6" s="19">
+      <c r="G6" s="17">
         <f t="shared" ref="G6:G11" si="3">E6*60+F6</f>
         <v>40</v>
       </c>
-      <c r="H6" s="13">
-        <f t="shared" ref="H6:H11" si="4">IF(HOUR(B6)&lt;=11,($B$2-$B$2*20%)/60,$B$2)</f>
+      <c r="H6" s="19">
+        <f t="shared" ref="H6:H11" si="4">IF(HOUR(B6)&lt;=11,($B$2-$B$2*20%)/60,$B$2/60)</f>
         <v>0.13333333333333333</v>
       </c>
-      <c r="I6" s="5"/>
+      <c r="I6" s="5">
+        <f t="shared" ref="I6:I11" si="5">G6*H6</f>
+        <v>5.333333333333333</v>
+      </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
@@ -759,23 +765,26 @@
         <f t="shared" si="0"/>
         <v>2.777777777777779E-2</v>
       </c>
-      <c r="E7" s="19">
+      <c r="E7" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F7" s="19">
+      <c r="F7" s="17">
         <f t="shared" si="2"/>
         <v>40</v>
       </c>
-      <c r="G7" s="19">
+      <c r="G7" s="17">
         <f t="shared" si="3"/>
         <v>40</v>
       </c>
-      <c r="H7" s="13">
+      <c r="H7" s="19">
         <f t="shared" si="4"/>
         <v>0.13333333333333333</v>
       </c>
-      <c r="I7" s="5"/>
+      <c r="I7" s="5">
+        <f t="shared" si="5"/>
+        <v>5.333333333333333</v>
+      </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
@@ -791,23 +800,26 @@
         <f t="shared" si="0"/>
         <v>2.3611111111111083E-2</v>
       </c>
-      <c r="E8" s="19">
+      <c r="E8" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F8" s="19">
+      <c r="F8" s="17">
         <f t="shared" si="2"/>
         <v>34</v>
       </c>
-      <c r="G8" s="19">
+      <c r="G8" s="17">
         <f t="shared" si="3"/>
         <v>34</v>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="19">
         <f t="shared" si="4"/>
         <v>0.13333333333333333</v>
       </c>
-      <c r="I8" s="5"/>
+      <c r="I8" s="5">
+        <f t="shared" si="5"/>
+        <v>4.5333333333333332</v>
+      </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
@@ -823,23 +835,26 @@
         <f t="shared" si="0"/>
         <v>6.8055555555555536E-2</v>
       </c>
-      <c r="E9" s="19">
+      <c r="E9" s="17">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="F9" s="19">
+      <c r="F9" s="17">
         <f t="shared" si="2"/>
         <v>38</v>
       </c>
-      <c r="G9" s="19">
+      <c r="G9" s="17">
         <f t="shared" si="3"/>
         <v>98</v>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="19">
         <f t="shared" si="4"/>
-        <v>10</v>
-      </c>
-      <c r="I9" s="5"/>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="I9" s="5">
+        <f t="shared" si="5"/>
+        <v>16.333333333333332</v>
+      </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
@@ -855,23 +870,26 @@
         <f t="shared" si="0"/>
         <v>0.11388888888888882</v>
       </c>
-      <c r="E10" s="19">
+      <c r="E10" s="17">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="F10" s="19">
+      <c r="F10" s="17">
         <f t="shared" si="2"/>
         <v>44</v>
       </c>
-      <c r="G10" s="19">
+      <c r="G10" s="17">
         <f t="shared" si="3"/>
         <v>164</v>
       </c>
-      <c r="H10" s="13">
+      <c r="H10" s="19">
         <f t="shared" si="4"/>
-        <v>10</v>
-      </c>
-      <c r="I10" s="5"/>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="I10" s="5">
+        <f t="shared" si="5"/>
+        <v>27.333333333333332</v>
+      </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
@@ -887,26 +905,29 @@
         <f t="shared" si="0"/>
         <v>5.208333333333337E-2</v>
       </c>
-      <c r="E11" s="19">
+      <c r="E11" s="17">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="F11" s="19">
+      <c r="F11" s="17">
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-      <c r="G11" s="19">
+      <c r="G11" s="17">
         <f t="shared" si="3"/>
         <v>75</v>
       </c>
-      <c r="H11" s="13">
+      <c r="H11" s="19">
         <f t="shared" si="4"/>
-        <v>10</v>
-      </c>
-      <c r="I11" s="5"/>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="I11" s="5">
+        <f t="shared" si="5"/>
+        <v>12.5</v>
+      </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C12" s="16">
+      <c r="C12" s="14">
         <f>SUM(C5:C11)</f>
         <v>3.8624999999999998</v>
       </c>
@@ -939,21 +960,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100CEB2B541769F8A4991DE642272C524BB" ma:contentTypeVersion="0" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="7ae862ae5010eca0394e8ac9f072291e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="397561fba88d9dece65508bac662637b">
     <xsd:element name="properties">
@@ -1067,24 +1073,22 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEC5D026-099B-4C5A-B95D-B86D765E2B2E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94AB0242-7A83-4BD2-8609-680DB457C9EC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3023F845-B776-44D6-BD9D-EB23702C7163}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1098,4 +1102,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94AB0242-7A83-4BD2-8609-680DB457C9EC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEC5D026-099B-4C5A-B95D-B86D765E2B2E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>